--- a/Excel/Vertical/hasil_gabungan_vertikal_Panjang Jalur Real.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Panjang Jalur Real.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Vertical\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F8EF75-4A93-4EFD-9CCD-42619456EA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -31,7 +37,7 @@
     <t>A*</t>
   </si>
   <si>
-    <t>JPS-BDS-GL-BRC-PPO</t>
+    <t>JPS-GL-BRC-PPO</t>
   </si>
   <si>
     <t>Map_1</t>
@@ -49,8 +55,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,13 +119,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -157,7 +171,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -191,6 +205,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -225,9 +240,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -400,11 +416,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -418,7 +434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -426,13 +442,13 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>24.14213562373095</v>
+        <v>24.142135623730951</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -440,13 +456,13 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>23.60406572566844</v>
+        <v>23.478510929252248</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -454,13 +470,13 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>49.698484809835</v>
+        <v>49.698484809835001</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -468,13 +484,13 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>48.09665262636237</v>
+        <v>48.671111236751813</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -488,7 +504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -496,13 +512,13 @@
         <v>64</v>
       </c>
       <c r="C7">
-        <v>97.22092897251733</v>
+        <v>98.691777601101194</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -516,7 +532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -524,13 +540,13 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>195.5180908545122</v>
+        <v>198.76982217329299</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -544,7 +560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -552,13 +568,13 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>24.83719391510835</v>
+        <v>25.719361685996219</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -566,13 +582,13 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>51.69848480983499</v>
+        <v>51.698484809834987</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -580,13 +596,13 @@
         <v>32</v>
       </c>
       <c r="C13">
-        <v>51.45450616521079</v>
+        <v>52.627005517466827</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -600,7 +616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -608,13 +624,13 @@
         <v>64</v>
       </c>
       <c r="C15">
-        <v>103.46142082518</v>
+        <v>105.96752212823171</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -622,13 +638,13 @@
         <v>128</v>
       </c>
       <c r="C16">
-        <v>208.5512985522207</v>
+        <v>208.55129855222069</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -636,13 +652,13 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>207.7489479300626</v>
+        <v>212.7549252358647</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -650,13 +666,13 @@
         <v>16</v>
       </c>
       <c r="C18">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -664,13 +680,13 @@
         <v>16</v>
       </c>
       <c r="C19">
-        <v>26.07496472499763</v>
+        <v>24.779271744364841</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -678,13 +694,13 @@
         <v>32</v>
       </c>
       <c r="C20">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -692,13 +708,13 @@
         <v>32</v>
       </c>
       <c r="C21">
-        <v>53.44654890763028</v>
+        <v>53.342193640088382</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -712,7 +728,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -720,13 +736,13 @@
         <v>64</v>
       </c>
       <c r="C23">
-        <v>106.8203763569287</v>
+        <v>107.95646521881891</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -734,13 +750,13 @@
         <v>128</v>
       </c>
       <c r="C24">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -748,13 +764,13 @@
         <v>128</v>
       </c>
       <c r="C25">
-        <v>214.3213788747858</v>
+        <v>216.49871687526471</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -768,7 +784,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -776,13 +792,13 @@
         <v>16</v>
       </c>
       <c r="C27">
-        <v>22.62089099732862</v>
+        <v>22.93245190266634</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -790,13 +806,13 @@
         <v>32</v>
       </c>
       <c r="C28">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="D28" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -804,13 +820,13 @@
         <v>32</v>
       </c>
       <c r="C29">
-        <v>46.75225471703789</v>
+        <v>47.27911736770578</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -818,13 +834,13 @@
         <v>64</v>
       </c>
       <c r="C30">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -832,13 +848,13 @@
         <v>64</v>
       </c>
       <c r="C31">
-        <v>94.9009341377288</v>
+        <v>95.972448297784652</v>
       </c>
       <c r="D31" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -846,13 +862,13 @@
         <v>128</v>
       </c>
       <c r="C32">
-        <v>198.350288425444</v>
+        <v>198.35028842544401</v>
       </c>
       <c r="D32" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -860,13 +876,13 @@
         <v>128</v>
       </c>
       <c r="C33">
-        <v>197.7247416993117</v>
+        <v>193.35911015794241</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -874,13 +890,13 @@
         <v>16</v>
       </c>
       <c r="C34">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -888,13 +904,13 @@
         <v>16</v>
       </c>
       <c r="C35">
-        <v>23.85486567281982</v>
+        <v>22.84376684661083</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -902,13 +918,13 @@
         <v>32</v>
       </c>
       <c r="C36">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -916,13 +932,13 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>47.71474284512288</v>
+        <v>46.699460933197493</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -930,13 +946,13 @@
         <v>64</v>
       </c>
       <c r="C38">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -944,13 +960,13 @@
         <v>64</v>
       </c>
       <c r="C39">
-        <v>95.50992475463946</v>
+        <v>94.485727508676931</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -964,7 +980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -972,7 +988,7 @@
         <v>128</v>
       </c>
       <c r="C41">
-        <v>192.2919197484023</v>
+        <v>190.09744533811039</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Panjang Jalur Real.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Panjang Jalur Real.xlsx
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>23.00389691313216</v>
+        <v>23.09901951359279</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -561,7 +561,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>46.99910636312252</v>
+        <v>46.86645192953345</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -631,7 +631,7 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>95.57049943528645</v>
+        <v>95.40233038888984</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -771,7 +771,7 @@
         <v>16</v>
       </c>
       <c r="C26">
-        <v>24.41488446708389</v>
+        <v>24.2748964148517</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
@@ -841,7 +841,7 @@
         <v>32</v>
       </c>
       <c r="C31">
-        <v>49.03946295574199</v>
+        <v>49.02879559762351</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -911,7 +911,7 @@
         <v>64</v>
       </c>
       <c r="C36">
-        <v>99.30085278599736</v>
+        <v>99.29815720118604</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
@@ -981,7 +981,7 @@
         <v>128</v>
       </c>
       <c r="C41">
-        <v>198.924964802366</v>
+        <v>198.9242808865375</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="C46">
-        <v>24.55639589508264</v>
+        <v>24.32285268768197</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -1121,7 +1121,7 @@
         <v>32</v>
       </c>
       <c r="C51">
-        <v>49.99028453499244</v>
+        <v>49.89643329835992</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -1191,7 +1191,7 @@
         <v>64</v>
       </c>
       <c r="C56">
-        <v>100.6498597519346</v>
+        <v>100.5452364519071</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
@@ -1261,7 +1261,7 @@
         <v>128</v>
       </c>
       <c r="C61">
-        <v>203.2060918012439</v>
+        <v>203.098893996986</v>
       </c>
       <c r="D61" t="s">
         <v>10</v>
@@ -1331,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="C66">
-        <v>22.57616073291973</v>
+        <v>22.56073125075471</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -1401,7 +1401,7 @@
         <v>32</v>
       </c>
       <c r="C71">
-        <v>46.54043818792906</v>
+        <v>46.64209787065961</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -1471,7 +1471,7 @@
         <v>64</v>
       </c>
       <c r="C76">
-        <v>92.90052844970226</v>
+        <v>92.69991043961832</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
@@ -1541,7 +1541,7 @@
         <v>128</v>
       </c>
       <c r="C81">
-        <v>190.4679384542775</v>
+        <v>190.5463808779157</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Panjang Jalur Real.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Panjang Jalur Real.xlsx
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>23.09901951359279</v>
+        <v>23.12310562561766</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -561,7 +561,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>46.86645192953345</v>
+        <v>47.00870142385959</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -589,7 +589,7 @@
         <v>64</v>
       </c>
       <c r="C13">
-        <v>103.2964645562817</v>
+        <v>102.4680374315355</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -631,7 +631,7 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>95.40233038888984</v>
+        <v>95.48180327461259</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -659,7 +659,7 @@
         <v>128</v>
       </c>
       <c r="C18">
-        <v>208.0071426749365</v>
+        <v>206.350288425444</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>16</v>
       </c>
       <c r="C23">
-        <v>28.38477631085023</v>
+        <v>25.55634918610405</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
@@ -771,7 +771,7 @@
         <v>16</v>
       </c>
       <c r="C26">
-        <v>24.2748964148517</v>
+        <v>24.370154202675</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
@@ -799,7 +799,7 @@
         <v>32</v>
       </c>
       <c r="C28">
-        <v>52.52691193458119</v>
+        <v>51.69848480983499</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
@@ -869,7 +869,7 @@
         <v>64</v>
       </c>
       <c r="C33">
-        <v>107.2964645562817</v>
+        <v>104.8111831820431</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -939,7 +939,7 @@
         <v>128</v>
       </c>
       <c r="C38">
-        <v>214.350288425444</v>
+        <v>211.8650070512055</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -1009,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C43">
-        <v>26.72792206135786</v>
+        <v>25.31370849898476</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="C46">
-        <v>24.32285268768197</v>
+        <v>24.54572853696417</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -1149,7 +1149,7 @@
         <v>64</v>
       </c>
       <c r="C53">
-        <v>106.3259018078045</v>
+        <v>108.6690475583121</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -1219,7 +1219,7 @@
         <v>128</v>
       </c>
       <c r="C58">
-        <v>214.0660171779821</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -1331,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="C66">
-        <v>22.56073125075471</v>
+        <v>22.73887683562801</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -1359,7 +1359,7 @@
         <v>32</v>
       </c>
       <c r="C68">
-        <v>50.18376618407358</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -1429,7 +1429,7 @@
         <v>64</v>
       </c>
       <c r="C73">
-        <v>102.3675323681472</v>
+        <v>100.953318805774</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -1499,7 +1499,7 @@
         <v>128</v>
       </c>
       <c r="C78">
-        <v>204.7350647362943</v>
+        <v>203.3208511739212</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -1779,7 +1779,7 @@
         <v>128</v>
       </c>
       <c r="C98">
-        <v>202.2497833620557</v>
+        <v>201.6639969244288</v>
       </c>
       <c r="D98" t="s">
         <v>12</v>
